--- a/demo/1_請求_2026年8月（下書き）.out（捨てた）.xlsx
+++ b/demo/1_請求_2026年8月（下書き）.out（捨てた）.xlsx
@@ -11,6 +11,14 @@
     <sheet name="8月請求" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="雛形" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="雛形_英文" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="確認★等しい" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="北斗精機" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="丸山工業" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="みどり建設" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="近江スチール" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="丸和物流" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="ヤマノ食品" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="検分" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="72">
   <si>
     <t xml:space="preserve">取引先</t>
   </si>
@@ -39,6 +47,9 @@
     <t xml:space="preserve">金額</t>
   </si>
   <si>
+    <t xml:space="preserve">税込み金額</t>
+  </si>
+  <si>
     <t xml:space="preserve">締め日</t>
   </si>
   <si>
@@ -48,27 +59,57 @@
     <t xml:space="preserve">確認</t>
   </si>
   <si>
+    <t xml:space="preserve">北斗精機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">精密部品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/08/31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鈴木</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★</t>
+  </si>
+  <si>
+    <t xml:space="preserve">丸山工業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCパーツ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佐藤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">みどり建設</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内装工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">近江スチール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼材加工</t>
+  </si>
+  <si>
+    <t xml:space="preserve">四角産業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">菊池</t>
+  </si>
+  <si>
     <t xml:space="preserve">丸和物流</t>
   </si>
   <si>
     <t xml:space="preserve">配送業務一式</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/08/31</t>
-  </si>
-  <si>
     <t xml:space="preserve">田中</t>
   </si>
   <si>
-    <t xml:space="preserve">近江スチール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鋼材加工</t>
-  </si>
-  <si>
-    <t xml:space="preserve">佐藤</t>
-  </si>
-  <si>
     <t xml:space="preserve">ヤマノ食品</t>
   </si>
   <si>
@@ -78,25 +119,7 @@
     <t xml:space="preserve">冷蔵配送</t>
   </si>
   <si>
-    <t xml:space="preserve">北斗精機</t>
-  </si>
-  <si>
-    <t xml:space="preserve">精密部品</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鈴木</t>
-  </si>
-  <si>
-    <t xml:space="preserve">丸山工業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCパーツ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">みどり建設</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内装工事</t>
+    <t xml:space="preserve">合計</t>
   </si>
   <si>
     <t xml:space="preserve">請　求　書</t>
@@ -603,6 +626,55 @@
   </si>
   <si>
     <t xml:space="preserve">Thank you for your business.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">パーツ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">シート名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">元の行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まとめた件数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,8</t>
   </si>
 </sst>
 </file>
@@ -809,8 +881,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -818,11 +894,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -887,6 +963,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1142,210 +1238,300 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="12.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="5.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="5.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
+      <c r="A2" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <f aca="false">E2*1.1</f>
+        <v>125400</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <f aca="false">E3*1.1</f>
+        <v>110000</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D4" s="5" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>64800</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <f aca="false">E4*1.1</f>
+        <v>71280</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <f aca="false">E5*1.1</f>
+        <v>66000</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <f aca="false">E6*1.1</f>
+        <v>121000</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>4800</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>57600</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F7" s="3" t="n">
+        <f aca="false">E7*1.1</f>
+        <v>63360</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>42000</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="F8" s="3" t="n">
+        <f aca="false">E8*1.1</f>
+        <v>46200</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="H8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>18000</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F9" s="3" t="n">
+        <f aca="false">E9*1.1</f>
+        <v>19800</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>38000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>114000</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>7200</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>64800</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="n">
+        <f aca="false">SUM(C2:INDEX(C:C,ROW()-1))</f>
+        <v>83</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <f aca="false">SUM(D2:INDEX(D:D,ROW()-1))</f>
+        <v>117500</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <f aca="false">SUM(E2:INDEX(E:E,ROW()-1))</f>
+        <v>566400</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <f aca="false">E10*1.1</f>
+        <v>623040</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1354,6 +1540,238 @@
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.82"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffffページ &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1366,99 +1784,99 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="20.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>29</v>
+      <c r="A3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>30</v>
+      <c r="A5" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>32</v>
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>33</v>
+      <c r="A9" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>38</v>
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>40</v>
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>41</v>
+      <c r="A14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>43</v>
+      <c r="A16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1483,85 +1901,85 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="21.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="21.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>44</v>
+      <c r="A1" s="16" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="10" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="10" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="B9" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>38</v>
+      <c r="C9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>55</v>
+      <c r="C11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>56</v>
+      <c r="A13" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1573,4 +1991,686 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="21" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffffページ &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>114000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>114000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>64800</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>64800</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="20.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>57600</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>57600</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>